--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2635" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Observation (Validated Result)</t>
+    <t>EU AI Generated Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile for clinical findings generated by an AI system, implementing LAW-02 (AI Flag) and linking to the AI Device.</t>
+    <t>An Observation profile representing a clinical output generated by an AI system, including AI-related transparency metadata and links to the relevant patient, encounter, and AI system.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -446,6 +446,9 @@
     <t>Observation.extension</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -484,6 +487,22 @@
   </si>
   <si>
     <t>The clinical reason why the AI was used for this specific patient.</t>
+  </si>
+  <si>
+    <t>Observation.extension:automatedDecision</t>
+  </si>
+  <si>
+    <t>automatedDecision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/automated-decision-flag}
+</t>
+  </si>
+  <si>
+    <t>Automated Decision-Making Flag</t>
+  </si>
+  <si>
+    <t>Indicates whether the AI-generated output was used as part of a solely automated decision-making process within the meaning of GDPR Article 22.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1994,12 +2013,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP67"/>
+  <dimension ref="A1:AP68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.58984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.93359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.19921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3019,7 +3038,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -3034,13 +3053,13 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3079,17 +3098,17 @@
         <v>18</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3101,7 +3120,7 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>18</v>
@@ -3124,13 +3143,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>18</v>
@@ -3140,7 +3159,7 @@
         <v>91</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>92</v>
@@ -3152,13 +3171,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3209,7 +3228,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3221,7 +3240,7 @@
         <v>18</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>18</v>
@@ -3242,48 +3261,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
         <v>155</v>
       </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>18</v>
       </c>
@@ -3331,7 +3348,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3343,7 +3360,7 @@
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>18</v>
@@ -3358,7 +3375,7 @@
         <v>18</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>18</v>
@@ -3366,14 +3383,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3386,21 +3403,23 @@
         <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
         <v>161</v>
       </c>
@@ -3451,7 +3470,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3463,22 +3482,22 @@
         <v>18</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>18</v>
@@ -3486,10 +3505,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3500,7 +3519,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>18</v>
@@ -3512,18 +3531,18 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -3571,13 +3590,13 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>18</v>
@@ -3586,19 +3605,19 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>18</v>
@@ -3606,21 +3625,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>18</v>
@@ -3632,18 +3651,18 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>178</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3691,13 +3710,13 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
@@ -3706,7 +3725,7 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>18</v>
@@ -3715,10 +3734,10 @@
         <v>18</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>18</v>
@@ -3726,14 +3745,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3749,19 +3768,21 @@
         <v>18</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>18</v>
       </c>
@@ -3809,7 +3830,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3824,7 +3845,7 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>18</v>
@@ -3833,10 +3854,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3844,10 +3865,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3858,7 +3879,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
@@ -3870,13 +3891,13 @@
         <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3927,19 +3948,19 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>18</v>
@@ -3951,10 +3972,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -3962,21 +3983,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
@@ -3988,7 +4009,7 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>194</v>
@@ -3996,9 +4017,7 @@
       <c r="M17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4053,13 +4072,13 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>18</v>
@@ -4074,7 +4093,7 @@
         <v>18</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>18</v>
@@ -4082,14 +4101,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4102,26 +4121,24 @@
         <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
       </c>
@@ -4169,7 +4186,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4181,7 +4198,7 @@
         <v>18</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>18</v>
@@ -4196,7 +4213,7 @@
         <v>18</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4204,42 +4221,46 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
@@ -4287,19 +4308,19 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>18</v>
@@ -4314,7 +4335,7 @@
         <v>18</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4322,10 +4343,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4348,13 +4369,13 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4381,13 +4402,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4405,7 +4426,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4451,7 +4472,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4463,10 +4484,10 @@
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>214</v>
@@ -4499,13 +4520,13 @@
         <v>18</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>18</v>
+        <v>216</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>18</v>
@@ -4526,7 +4547,7 @@
         <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4550,7 +4571,7 @@
         <v>18</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4558,21 +4579,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4581,10 +4602,10 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>220</v>
@@ -4592,9 +4613,7 @@
       <c r="M22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4643,13 +4662,13 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
@@ -4658,66 +4677,64 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>111</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
@@ -4741,13 +4758,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -4765,13 +4782,13 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>18</v>
@@ -4780,19 +4797,19 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4800,10 +4817,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4811,34 +4828,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4863,13 +4880,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4887,13 +4904,13 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>18</v>
@@ -4902,65 +4919,65 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>18</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -4985,13 +5002,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -5009,49 +5026,49 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>259</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>18</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>263</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5070,19 +5087,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -5107,13 +5124,13 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
@@ -5131,45 +5148,45 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5177,13 +5194,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -5192,18 +5209,20 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
       </c>
@@ -5251,13 +5270,13 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>18</v>
@@ -5266,16 +5285,16 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>279</v>
@@ -5293,14 +5312,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -5312,20 +5331,18 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5379,7 +5396,7 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
@@ -5388,44 +5405,44 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -5434,19 +5451,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5495,7 +5512,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5510,44 +5527,44 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>18</v>
+        <v>298</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -5556,18 +5573,20 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -5615,7 +5634,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5630,19 +5649,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>18</v>
+        <v>304</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>18</v>
@@ -5650,10 +5669,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5664,7 +5683,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>18</v>
@@ -5676,18 +5695,18 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>314</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5735,13 +5754,13 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>18</v>
@@ -5750,19 +5769,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>18</v>
@@ -5770,10 +5789,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5784,7 +5803,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -5796,19 +5815,17 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5857,45 +5874,45 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>18</v>
+        <v>322</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>329</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5915,22 +5932,22 @@
         <v>18</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5955,13 +5972,13 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>336</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>337</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
@@ -5979,7 +5996,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5988,7 +6005,7 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
@@ -6000,38 +6017,38 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>18</v>
+        <v>332</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>136</v>
+        <v>333</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>18</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>341</v>
+        <v>18</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -6040,19 +6057,19 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -6077,38 +6094,40 @@
         <v>18</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>18</v>
+        <v>344</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>103</v>
@@ -6120,40 +6139,38 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>349</v>
+        <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>350</v>
+        <v>136</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>352</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>18</v>
@@ -6162,19 +6179,19 @@
         <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
@@ -6199,31 +6216,29 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AC35" s="2"/>
+      <c r="AD35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6244,38 +6259,40 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -6284,16 +6301,20 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>93</v>
+        <v>245</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>361</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6317,13 +6338,13 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>18</v>
+        <v>341</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>18</v>
+        <v>352</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>18</v>
+        <v>353</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -6341,19 +6362,19 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>190</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>18</v>
@@ -6362,35 +6383,35 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>18</v>
+        <v>356</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>192</v>
+        <v>357</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>18</v>
+        <v>358</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -6402,7 +6423,7 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>194</v>
@@ -6410,9 +6431,7 @@
       <c r="M37" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="N37" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6449,16 +6468,16 @@
         <v>18</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>360</v>
+        <v>18</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>196</v>
@@ -6467,13 +6486,13 @@
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>18</v>
@@ -6488,7 +6507,7 @@
         <v>18</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>18</v>
@@ -6496,18 +6515,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>79</v>
@@ -6519,23 +6538,21 @@
         <v>18</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>363</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>200</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>201</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6544,7 +6561,7 @@
         <v>18</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>18</v>
@@ -6571,19 +6588,19 @@
         <v>18</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>18</v>
+        <v>366</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>202</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6595,7 +6612,7 @@
         <v>18</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>18</v>
@@ -6607,10 +6624,10 @@
         <v>18</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>370</v>
+        <v>18</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>371</v>
+        <v>198</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>18</v>
@@ -6618,10 +6635,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6629,10 +6646,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
@@ -6644,19 +6661,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>187</v>
+        <v>369</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6666,7 +6683,7 @@
         <v>18</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>18</v>
+        <v>374</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>18</v>
@@ -6705,13 +6722,13 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>18</v>
@@ -6729,10 +6746,10 @@
         <v>18</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>18</v>
@@ -6740,10 +6757,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6754,7 +6771,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6763,22 +6780,22 @@
         <v>18</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6827,13 +6844,13 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
@@ -6851,10 +6868,10 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>18</v>
@@ -6862,10 +6879,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6876,7 +6893,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6888,18 +6905,20 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>239</v>
+        <v>388</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
       </c>
@@ -6923,13 +6942,13 @@
         <v>18</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>393</v>
+        <v>18</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>394</v>
+        <v>18</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>18</v>
@@ -6947,16 +6966,16 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>103</v>
@@ -6968,24 +6987,24 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>399</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7008,16 +7027,16 @@
         <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>401</v>
+        <v>245</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7043,13 +7062,13 @@
         <v>18</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>18</v>
+        <v>399</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>18</v>
@@ -7067,7 +7086,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7076,7 +7095,7 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -7088,24 +7107,24 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>18</v>
+        <v>402</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>18</v>
+        <v>403</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7128,20 +7147,18 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>239</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>18</v>
       </c>
@@ -7165,13 +7182,13 @@
         <v>18</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>410</v>
+        <v>18</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>18</v>
@@ -7189,7 +7206,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7198,7 +7215,7 @@
         <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>18</v>
+        <v>401</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
@@ -7213,10 +7230,10 @@
         <v>18</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>412</v>
+        <v>18</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>18</v>
@@ -7224,10 +7241,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7250,18 +7267,20 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
       </c>
@@ -7285,13 +7304,13 @@
         <v>18</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>18</v>
+        <v>416</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>18</v>
@@ -7309,7 +7328,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7321,33 +7340,33 @@
         <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7355,13 +7374,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -7370,16 +7389,16 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7429,7 +7448,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7441,7 +7460,7 @@
         <v>18</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>425</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>18</v>
@@ -7450,24 +7469,24 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AN45" t="s" s="2">
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AO45" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7475,13 +7494,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -7490,20 +7509,18 @@
         <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>183</v>
+        <v>431</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>437</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7551,45 +7568,45 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7600,7 +7617,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
@@ -7612,16 +7629,20 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>188</v>
+        <v>440</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
       </c>
@@ -7669,19 +7690,19 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>190</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>18</v>
+        <v>444</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
@@ -7693,10 +7714,10 @@
         <v>18</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>18</v>
+        <v>445</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>192</v>
+        <v>446</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>18</v>
@@ -7704,21 +7725,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -7730,7 +7751,7 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>194</v>
@@ -7738,9 +7759,7 @@
       <c r="M48" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7795,13 +7814,13 @@
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
@@ -7816,7 +7835,7 @@
         <v>18</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>18</v>
@@ -7824,14 +7843,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7844,26 +7863,24 @@
         <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>18</v>
       </c>
@@ -7911,7 +7928,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7923,7 +7940,7 @@
         <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
@@ -7938,7 +7955,7 @@
         <v>18</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>18</v>
@@ -7946,42 +7963,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>445</v>
+        <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>205</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8029,19 +8050,19 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>207</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
@@ -8053,10 +8074,10 @@
         <v>18</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>439</v>
+        <v>18</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>449</v>
+        <v>136</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>18</v>
@@ -8090,13 +8111,13 @@
         <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8156,7 +8177,7 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>103</v>
@@ -8171,10 +8192,10 @@
         <v>18</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>18</v>
@@ -8182,10 +8203,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8208,13 +8229,13 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>239</v>
+        <v>451</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8241,13 +8262,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>457</v>
+        <v>18</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>458</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -8265,7 +8286,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8274,7 +8295,7 @@
         <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>18</v>
+        <v>454</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -8289,7 +8310,7 @@
         <v>18</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>459</v>
@@ -8326,7 +8347,7 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>461</v>
@@ -8334,12 +8355,8 @@
       <c r="M53" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N53" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>464</v>
-      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -8363,13 +8380,13 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>18</v>
@@ -8408,13 +8425,13 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>467</v>
+        <v>18</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>18</v>
@@ -8422,10 +8439,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8436,7 +8453,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>18</v>
@@ -8448,19 +8465,19 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8485,13 +8502,13 @@
         <v>18</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>18</v>
@@ -8509,13 +8526,13 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>18</v>
@@ -8530,13 +8547,13 @@
         <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>18</v>
@@ -8544,10 +8561,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8558,7 +8575,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>18</v>
@@ -8570,17 +8587,19 @@
         <v>18</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8605,13 +8624,13 @@
         <v>18</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>18</v>
+        <v>480</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
@@ -8629,13 +8648,13 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>18</v>
@@ -8650,13 +8669,13 @@
         <v>18</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>18</v>
+        <v>473</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>18</v>
+        <v>474</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>481</v>
+        <v>357</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>18</v>
@@ -8699,7 +8718,9 @@
         <v>485</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8756,7 +8777,7 @@
         <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>103</v>
@@ -8771,10 +8792,10 @@
         <v>18</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>439</v>
+        <v>18</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>18</v>
@@ -8782,10 +8803,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8796,7 +8817,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8805,20 +8826,18 @@
         <v>18</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N57" t="s" s="2">
         <v>491</v>
       </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8867,16 +8886,16 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>18</v>
+        <v>454</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>103</v>
@@ -8891,10 +8910,10 @@
         <v>18</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -9011,10 +9030,10 @@
         <v>18</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>498</v>
+        <v>212</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>18</v>
@@ -9048,20 +9067,18 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>183</v>
+        <v>500</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O59" t="s" s="2">
         <v>503</v>
       </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9118,7 +9135,7 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>103</v>
@@ -9133,10 +9150,10 @@
         <v>18</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>18</v>
@@ -9144,10 +9161,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9158,7 +9175,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>18</v>
@@ -9167,19 +9184,23 @@
         <v>18</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>188</v>
+        <v>506</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9227,19 +9248,19 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>190</v>
+        <v>505</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>18</v>
@@ -9251,10 +9272,10 @@
         <v>18</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>18</v>
+        <v>510</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>192</v>
+        <v>511</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>18</v>
@@ -9262,21 +9283,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
@@ -9288,7 +9309,7 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>194</v>
@@ -9296,9 +9317,7 @@
       <c r="M61" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9353,13 +9372,13 @@
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>18</v>
@@ -9374,7 +9393,7 @@
         <v>18</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>18</v>
@@ -9382,14 +9401,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9402,26 +9421,24 @@
         <v>18</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>18</v>
       </c>
@@ -9469,7 +9486,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9481,7 +9498,7 @@
         <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>18</v>
@@ -9496,7 +9513,7 @@
         <v>18</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>18</v>
@@ -9504,45 +9521,45 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>239</v>
+        <v>139</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>510</v>
+        <v>205</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>511</v>
+        <v>206</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>512</v>
+        <v>160</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>254</v>
+        <v>161</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>18</v>
@@ -9567,13 +9584,13 @@
         <v>18</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>257</v>
+        <v>18</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>18</v>
@@ -9591,34 +9608,34 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>509</v>
+        <v>207</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>513</v>
+        <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>18</v>
@@ -9626,10 +9643,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9637,7 +9654,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>91</v>
@@ -9652,19 +9669,19 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>322</v>
+        <v>517</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>324</v>
+        <v>260</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>18</v>
@@ -9689,13 +9706,13 @@
         <v>18</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
@@ -9713,16 +9730,16 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -9731,27 +9748,27 @@
         <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>328</v>
+        <v>218</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>329</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9771,22 +9788,22 @@
         <v>18</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>520</v>
+        <v>328</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9811,13 +9828,13 @@
         <v>18</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>336</v>
+        <v>18</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>337</v>
+        <v>18</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>18</v>
@@ -9835,7 +9852,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9856,35 +9873,35 @@
         <v>18</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>18</v>
+        <v>523</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>136</v>
+        <v>333</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>18</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>341</v>
+        <v>18</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>18</v>
@@ -9896,19 +9913,19 @@
         <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>342</v>
+        <v>525</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>343</v>
+        <v>526</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>344</v>
+        <v>527</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -9933,13 +9950,13 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
@@ -9957,13 +9974,13 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>18</v>
@@ -9978,28 +9995,28 @@
         <v>18</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>349</v>
+        <v>18</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>350</v>
+        <v>136</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>352</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10018,19 +10035,19 @@
         <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>524</v>
+        <v>348</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>525</v>
+        <v>349</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>436</v>
+        <v>350</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10055,13 +10072,13 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>18</v>
+        <v>341</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>18</v>
+        <v>352</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>18</v>
+        <v>353</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
@@ -10079,7 +10096,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10100,20 +10117,142 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>440</v>
+        <v>357</v>
       </c>
       <c r="AP67" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP67">
+  <autoFilter ref="A1:AP68">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10123,7 +10262,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI66">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -483,10 +483,10 @@
 </t>
   </si>
   <si>
-    <t>Case-Specific Indication</t>
-  </si>
-  <si>
-    <t>The clinical reason why the AI was used for this specific patient.</t>
+    <t>Clinical reason for AI use</t>
+  </si>
+  <si>
+    <t>Records the clinical indication or case-specific reason for applying the AI system in the documented patient context.</t>
   </si>
   <si>
     <t>Observation.extension:automatedDecision</t>
@@ -499,10 +499,10 @@
 </t>
   </si>
   <si>
-    <t>Automated Decision-Making Flag</t>
-  </si>
-  <si>
-    <t>Indicates whether the AI-generated output was used as part of a solely automated decision-making process within the meaning of GDPR Article 22.</t>
+    <t>Automated decision flag</t>
+  </si>
+  <si>
+    <t>Indicates whether the documented AI-supported processing resulted in a decision made solely by automated means.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -751,7 +751,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>Workflow state: preliminary (unseen) | final (checked) | entered-in-error (overridden)</t>
+    <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -1201,7 +1201,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem"/&gt;
+  &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-involvement-cs"/&gt;
   &lt;code value="ai-generated"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
@@ -5059,7 +5059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>255</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
